--- a/esyluban/examples/dev/DataTables/negatives/path_fail.xlsx
+++ b/esyluban/examples/dev/DataTables/negatives/path_fail.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>full_name="matrix.TbPathFail" &amp; value_type="matrix.PathRecord" &amp; index="id" &amp; mode="map" &amp; read_schema_from_file="false" &amp; group="t" &amp; output="matrix_tbpathfail"</t>
+          <t>full_name="matrix.TbPathFail" &amp; value_type="matrix.PathRecord" &amp; index="id" &amp; group="t"</t>
         </is>
       </c>
     </row>
